--- a/astro-site/public/dl/taco-shop-checklist-templates/05-taqueria-manager-checklist.xlsx
+++ b/astro-site/public/dl/taco-shop-checklist-templates/05-taqueria-manager-checklist.xlsx
@@ -962,7 +962,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Review the shift's reservations and large-party forecast</t>
+          <t>Review the shift's catering and large-order forecast</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
